--- a/Reference/Mitigations Tests.xlsx
+++ b/Reference/Mitigations Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\tdm-ghg-calculator\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA30406-65FF-4BF6-B16F-1D2A345597A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CACA21-E4C1-44B9-AC6D-1D222A9D4844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="5010" windowWidth="19200" windowHeight="8670" firstSheet="31" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="18" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="T1" sheetId="1" r:id="rId1"/>
@@ -32,24 +32,27 @@
     <sheet name="T16" sheetId="16" r:id="rId17"/>
     <sheet name="T17" sheetId="17" r:id="rId18"/>
     <sheet name="T18" sheetId="18" r:id="rId19"/>
-    <sheet name="T20" sheetId="28" r:id="rId20"/>
-    <sheet name="T21a" sheetId="19" r:id="rId21"/>
-    <sheet name="T22a" sheetId="29" r:id="rId22"/>
-    <sheet name="T22b" sheetId="30" r:id="rId23"/>
-    <sheet name="T22c" sheetId="32" r:id="rId24"/>
-    <sheet name="T22d" sheetId="31" r:id="rId25"/>
-    <sheet name="T21b" sheetId="20" r:id="rId26"/>
-    <sheet name="T22cB" sheetId="21" r:id="rId27"/>
-    <sheet name="T23" sheetId="22" r:id="rId28"/>
-    <sheet name="T24B" sheetId="23" r:id="rId29"/>
-    <sheet name="T25B" sheetId="24" r:id="rId30"/>
-    <sheet name="T26" sheetId="25" r:id="rId31"/>
-    <sheet name="T27" sheetId="27" r:id="rId32"/>
-    <sheet name="T28" sheetId="33" r:id="rId33"/>
-    <sheet name="T29B" sheetId="34" r:id="rId34"/>
-    <sheet name="T40" sheetId="36" r:id="rId35"/>
-    <sheet name="T46" sheetId="35" r:id="rId36"/>
-    <sheet name="T56" sheetId="37" r:id="rId37"/>
+    <sheet name="T19A" sheetId="39" r:id="rId20"/>
+    <sheet name="T19B" sheetId="40" r:id="rId21"/>
+    <sheet name="T20" sheetId="28" r:id="rId22"/>
+    <sheet name="T21a" sheetId="19" r:id="rId23"/>
+    <sheet name="T22a" sheetId="29" r:id="rId24"/>
+    <sheet name="T22b" sheetId="30" r:id="rId25"/>
+    <sheet name="T22c" sheetId="32" r:id="rId26"/>
+    <sheet name="T22d" sheetId="31" r:id="rId27"/>
+    <sheet name="T21b" sheetId="20" r:id="rId28"/>
+    <sheet name="T22cB" sheetId="21" r:id="rId29"/>
+    <sheet name="T23" sheetId="22" r:id="rId30"/>
+    <sheet name="T24B" sheetId="23" r:id="rId31"/>
+    <sheet name="T25B" sheetId="24" r:id="rId32"/>
+    <sheet name="T26" sheetId="25" r:id="rId33"/>
+    <sheet name="T27" sheetId="27" r:id="rId34"/>
+    <sheet name="T28" sheetId="33" r:id="rId35"/>
+    <sheet name="T29B" sheetId="34" r:id="rId36"/>
+    <sheet name="T30" sheetId="38" r:id="rId37"/>
+    <sheet name="T40" sheetId="36" r:id="rId38"/>
+    <sheet name="T46" sheetId="35" r:id="rId39"/>
+    <sheet name="T56" sheetId="37" r:id="rId40"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="12">
   <si>
     <t>B</t>
   </si>
@@ -1146,32 +1149,32 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6860669-536E-478F-9C8D-4895DCFE63A0}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>0.03</v>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D43674-F8CA-4892-9418-1EB2C684B669}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2.07E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1179,7 +1182,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.85</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1187,7 +1190,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2.2999999999999998</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1195,7 +1198,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1203,6 +1206,156 @@
         <v>7</v>
       </c>
       <c r="B7">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <f>-B1*(((B5/B8)*(B2+B3)*B4*B6)/B7)</f>
+        <v>-4.0837211763227344E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE75B56-B57D-40E3-B6D5-EF484BAA8BB4}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>0.86599999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>-B1*((((B3*(B5-(B2*B5)))/(B4*B6))))</f>
+        <v>1.265378962838546E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6860669-536E-478F-9C8D-4895DCFE63A0}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
         <v>0.25</v>
       </c>
     </row>
@@ -1220,7 +1373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788757BC-5CD0-428B-BD1C-3A13CCA94843}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1272,7 +1425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADB945E-76DD-4F0B-9374-A0D4D5770EE9}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1348,7 +1501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB0BC64-71B3-4F79-95ED-EE6427AF4050}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1424,7 +1577,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953B5401-36F7-4AFE-839C-026FA056AD0B}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1499,7 +1652,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{027E8AEE-0803-4B02-9E46-BDF34BF75B33}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1591,7 +1744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8988892F-DED0-46F4-AA2C-CCF2CC1ADF7C}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1686,7 +1839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD9EE00-52A7-487E-921D-B9FCCC55DCBC}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1762,7 +1915,50 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>-(B2*B1)/B3</f>
+        <v>-0.21777777777777779</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0D036EF-8CF1-4C13-9B46-8108C0132C37}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1821,7 +2017,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105B05B6-310E-40FF-A289-A462CFD2CD1A}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1897,50 +2093,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56180196-4A51-42CE-9237-42DECB8F409D}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <f>-(B2*B1)/B3</f>
-        <v>-0.21777777777777779</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5EE5C2E-1F2E-408A-BC54-0F14E725BF63}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2007,7 +2160,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5EF6D2-2159-4E97-8BF0-19BB3D566A71}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2074,7 +2227,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E4C011-9C8B-4490-8B6D-F742F24FB084}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2141,7 +2294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03489F6D-C13B-4D2F-B889-50C72227FDF1}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2233,7 +2386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D4371F-7752-4380-AAD2-3CD65C64C4E4}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2301,7 +2454,50 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD0B3FF-71A9-44B4-A1C6-45B681ED2EB7}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>B1*((B2-B3)/B3)</f>
+        <v>-0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9A9924-ECD5-42C9-AEB6-442F006B5576}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2385,7 +2581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1BA039-FAE9-4F58-A255-BAD81FF0BAAA}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2451,7 +2647,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.158</v>
+        <v>0.20300000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -2468,7 +2664,7 @@
       </c>
       <c r="B10">
         <f>B1*(B2/B3)*B4*(B5/B6)*(B7-B8)*B9</f>
-        <v>-1.4115041379310343E-3</v>
+        <v>-7.1350758620689623E-4</v>
       </c>
     </row>
   </sheetData>
@@ -2477,7 +2673,42 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D486991-6FF1-4805-9025-F98917C073B8}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-0.28599999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>B2*B1</f>
+        <v>-5.7200000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83802985-441C-4BBF-B305-3743B0992738}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2544,41 +2775,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D486991-6FF1-4805-9025-F98917C073B8}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>-0.28599999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <f>B2*B1</f>
-        <v>-5.7200000000000001E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5ED6D57-DE29-4DAC-A3AA-80DD11128A92}">
   <dimension ref="A1:B4"/>
